--- a/20_設計書/管理者申請ログ確認画面.xlsx
+++ b/20_設計書/管理者申請ログ確認画面.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AMA1040\Documents\古竹作成\基本設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E1C58FC-A4D4-4F91-8F5F-F772706F32AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8219AABC-D2C9-4C69-9A7F-FA7DD73369B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30510" yWindow="1710" windowWidth="16245" windowHeight="10095" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -197,7 +197,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="151">
   <si>
     <t>HRS殿</t>
     <rPh sb="3" eb="4">
@@ -1253,6 +1253,23 @@
   </si>
   <si>
     <t>dr1.2</t>
+    <phoneticPr fontId="51"/>
+  </si>
+  <si>
+    <t>dr1.3</t>
+    <phoneticPr fontId="51"/>
+  </si>
+  <si>
+    <t>課題リストの回答をもとに修正</t>
+    <rPh sb="0" eb="2">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シュウセイ</t>
+    </rPh>
     <phoneticPr fontId="51"/>
   </si>
 </sst>
@@ -4595,640 +4612,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>50</xdr:col>
-      <xdr:colOff>38560</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>51</xdr:col>
-      <xdr:colOff>96157</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>82550</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="43" name="グループ化 42">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{190F2F8F-F26B-D4C4-428B-F09994C239EE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="9034393" y="3920067"/>
-          <a:ext cx="237514" cy="3944408"/>
-          <a:chOff x="9168639" y="1937727"/>
-          <a:chExt cx="240770" cy="3921613"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="16" name="図 15">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B21E0430-3E48-64BE-F460-672D2AD66092}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm flipH="1">
-            <a:off x="9177705" y="1937727"/>
-            <a:ext cx="221273" cy="1291736"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="18" name="図 17">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40647910-157D-4CCD-9218-37552E8E1E2F}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill rotWithShape="1">
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-          <a:srcRect l="1" t="75912" r="-1"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm flipH="1">
-            <a:off x="9190403" y="5543306"/>
-            <a:ext cx="218098" cy="316034"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="24" name="グループ化 23">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A89C33FA-1A55-BC59-6412-F6CC901DB773}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="9186778" y="4750047"/>
-            <a:ext cx="219456" cy="814126"/>
-            <a:chOff x="9212945" y="4758421"/>
-            <a:chExt cx="219980" cy="824592"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:grpSp>
-          <xdr:nvGrpSpPr>
-            <xdr:cNvPr id="20" name="グループ化 19">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE300F40-3C8C-2723-043D-EBAA6D6043BB}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGrpSpPr/>
-          </xdr:nvGrpSpPr>
-          <xdr:grpSpPr>
-            <a:xfrm>
-              <a:off x="9210676" y="5174341"/>
-              <a:ext cx="225424" cy="408672"/>
-              <a:chOff x="9210676" y="5174341"/>
-              <a:chExt cx="225424" cy="408672"/>
-            </a:xfrm>
-          </xdr:grpSpPr>
-          <xdr:pic>
-            <xdr:nvPicPr>
-              <xdr:cNvPr id="17" name="図 16">
-                <a:extLst>
-                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6209DF18-0471-4A53-883B-360416A15FF4}"/>
-                  </a:ext>
-                </a:extLst>
-              </xdr:cNvPr>
-              <xdr:cNvPicPr>
-                <a:picLocks noChangeAspect="1"/>
-              </xdr:cNvPicPr>
-            </xdr:nvPicPr>
-            <xdr:blipFill rotWithShape="1">
-              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-              <a:srcRect t="75912" r="-4286" b="6391"/>
-              <a:stretch>
-                <a:fillRect/>
-              </a:stretch>
-            </xdr:blipFill>
-            <xdr:spPr>
-              <a:xfrm flipH="1">
-                <a:off x="9213851" y="5354866"/>
-                <a:ext cx="222249" cy="228147"/>
-              </a:xfrm>
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
-            </xdr:spPr>
-          </xdr:pic>
-          <xdr:pic>
-            <xdr:nvPicPr>
-              <xdr:cNvPr id="19" name="図 18">
-                <a:extLst>
-                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB8B9517-BC3E-4641-96A8-7DB256091C16}"/>
-                  </a:ext>
-                </a:extLst>
-              </xdr:cNvPr>
-              <xdr:cNvPicPr>
-                <a:picLocks noChangeAspect="1"/>
-              </xdr:cNvPicPr>
-            </xdr:nvPicPr>
-            <xdr:blipFill rotWithShape="1">
-              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-              <a:srcRect t="75912" r="-4286" b="6391"/>
-              <a:stretch>
-                <a:fillRect/>
-              </a:stretch>
-            </xdr:blipFill>
-            <xdr:spPr>
-              <a:xfrm flipH="1">
-                <a:off x="9210676" y="5174341"/>
-                <a:ext cx="225424" cy="224972"/>
-              </a:xfrm>
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
-            </xdr:spPr>
-          </xdr:pic>
-        </xdr:grpSp>
-        <xdr:grpSp>
-          <xdr:nvGrpSpPr>
-            <xdr:cNvPr id="21" name="グループ化 20">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{902749EB-42E2-4211-8E40-54EEBA6ED787}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGrpSpPr/>
-          </xdr:nvGrpSpPr>
-          <xdr:grpSpPr>
-            <a:xfrm>
-              <a:off x="9216120" y="4755246"/>
-              <a:ext cx="209549" cy="418197"/>
-              <a:chOff x="9210676" y="5174341"/>
-              <a:chExt cx="225424" cy="408672"/>
-            </a:xfrm>
-          </xdr:grpSpPr>
-          <xdr:pic>
-            <xdr:nvPicPr>
-              <xdr:cNvPr id="22" name="図 21">
-                <a:extLst>
-                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6ACEA208-2950-C167-2275-27316F07B70F}"/>
-                  </a:ext>
-                </a:extLst>
-              </xdr:cNvPr>
-              <xdr:cNvPicPr>
-                <a:picLocks noChangeAspect="1"/>
-              </xdr:cNvPicPr>
-            </xdr:nvPicPr>
-            <xdr:blipFill rotWithShape="1">
-              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-              <a:srcRect t="75912" r="-4286" b="6391"/>
-              <a:stretch>
-                <a:fillRect/>
-              </a:stretch>
-            </xdr:blipFill>
-            <xdr:spPr>
-              <a:xfrm flipH="1">
-                <a:off x="9213851" y="5354866"/>
-                <a:ext cx="222249" cy="228147"/>
-              </a:xfrm>
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
-            </xdr:spPr>
-          </xdr:pic>
-          <xdr:pic>
-            <xdr:nvPicPr>
-              <xdr:cNvPr id="23" name="図 22">
-                <a:extLst>
-                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25D2B1D6-7DB4-83F1-A16E-028537F9F6A2}"/>
-                  </a:ext>
-                </a:extLst>
-              </xdr:cNvPr>
-              <xdr:cNvPicPr>
-                <a:picLocks noChangeAspect="1"/>
-              </xdr:cNvPicPr>
-            </xdr:nvPicPr>
-            <xdr:blipFill rotWithShape="1">
-              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-              <a:srcRect t="75912" r="-4286" b="6391"/>
-              <a:stretch>
-                <a:fillRect/>
-              </a:stretch>
-            </xdr:blipFill>
-            <xdr:spPr>
-              <a:xfrm flipH="1">
-                <a:off x="9210676" y="5174341"/>
-                <a:ext cx="225424" cy="224972"/>
-              </a:xfrm>
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
-            </xdr:spPr>
-          </xdr:pic>
-        </xdr:grpSp>
-      </xdr:grpSp>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="26" name="グループ化 25">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19C6AE78-C4E8-4EAA-B7E3-167B307E03FB}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="9175896" y="3940040"/>
-            <a:ext cx="235331" cy="817718"/>
-            <a:chOff x="9212945" y="4758421"/>
-            <a:chExt cx="219980" cy="824592"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:grpSp>
-          <xdr:nvGrpSpPr>
-            <xdr:cNvPr id="27" name="グループ化 26">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAB3112D-8A22-094C-B73B-71E4B2C95AE9}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGrpSpPr/>
-          </xdr:nvGrpSpPr>
-          <xdr:grpSpPr>
-            <a:xfrm>
-              <a:off x="9210676" y="5174341"/>
-              <a:ext cx="225424" cy="408672"/>
-              <a:chOff x="9210676" y="5174341"/>
-              <a:chExt cx="225424" cy="408672"/>
-            </a:xfrm>
-          </xdr:grpSpPr>
-          <xdr:pic>
-            <xdr:nvPicPr>
-              <xdr:cNvPr id="34" name="図 33">
-                <a:extLst>
-                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E6C6FDC-7721-22B7-8F10-4E3C8A5051E4}"/>
-                  </a:ext>
-                </a:extLst>
-              </xdr:cNvPr>
-              <xdr:cNvPicPr>
-                <a:picLocks noChangeAspect="1"/>
-              </xdr:cNvPicPr>
-            </xdr:nvPicPr>
-            <xdr:blipFill rotWithShape="1">
-              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-              <a:srcRect t="75912" r="-4286" b="6391"/>
-              <a:stretch>
-                <a:fillRect/>
-              </a:stretch>
-            </xdr:blipFill>
-            <xdr:spPr>
-              <a:xfrm flipH="1">
-                <a:off x="9213851" y="5354866"/>
-                <a:ext cx="222249" cy="228147"/>
-              </a:xfrm>
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
-            </xdr:spPr>
-          </xdr:pic>
-          <xdr:pic>
-            <xdr:nvPicPr>
-              <xdr:cNvPr id="35" name="図 34">
-                <a:extLst>
-                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{378260FB-D957-106D-CF12-3CF9C60E216A}"/>
-                  </a:ext>
-                </a:extLst>
-              </xdr:cNvPr>
-              <xdr:cNvPicPr>
-                <a:picLocks noChangeAspect="1"/>
-              </xdr:cNvPicPr>
-            </xdr:nvPicPr>
-            <xdr:blipFill rotWithShape="1">
-              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-              <a:srcRect t="75912" r="-4286" b="6391"/>
-              <a:stretch>
-                <a:fillRect/>
-              </a:stretch>
-            </xdr:blipFill>
-            <xdr:spPr>
-              <a:xfrm flipH="1">
-                <a:off x="9210676" y="5174341"/>
-                <a:ext cx="225424" cy="224972"/>
-              </a:xfrm>
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
-            </xdr:spPr>
-          </xdr:pic>
-        </xdr:grpSp>
-        <xdr:grpSp>
-          <xdr:nvGrpSpPr>
-            <xdr:cNvPr id="28" name="グループ化 27">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A014C297-24E8-A19E-D1CA-6923386E749B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGrpSpPr/>
-          </xdr:nvGrpSpPr>
-          <xdr:grpSpPr>
-            <a:xfrm>
-              <a:off x="9216120" y="4755246"/>
-              <a:ext cx="209549" cy="418197"/>
-              <a:chOff x="9210676" y="5174341"/>
-              <a:chExt cx="225424" cy="408672"/>
-            </a:xfrm>
-          </xdr:grpSpPr>
-          <xdr:pic>
-            <xdr:nvPicPr>
-              <xdr:cNvPr id="29" name="図 28">
-                <a:extLst>
-                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{487BB4F3-B71D-5048-9875-12387967A56D}"/>
-                  </a:ext>
-                </a:extLst>
-              </xdr:cNvPr>
-              <xdr:cNvPicPr>
-                <a:picLocks noChangeAspect="1"/>
-              </xdr:cNvPicPr>
-            </xdr:nvPicPr>
-            <xdr:blipFill rotWithShape="1">
-              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-              <a:srcRect t="75912" r="-4286" b="6391"/>
-              <a:stretch>
-                <a:fillRect/>
-              </a:stretch>
-            </xdr:blipFill>
-            <xdr:spPr>
-              <a:xfrm flipH="1">
-                <a:off x="9213851" y="5354866"/>
-                <a:ext cx="222249" cy="228147"/>
-              </a:xfrm>
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
-            </xdr:spPr>
-          </xdr:pic>
-          <xdr:pic>
-            <xdr:nvPicPr>
-              <xdr:cNvPr id="31" name="図 30">
-                <a:extLst>
-                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4143FE76-3775-AD45-1B7A-830E9357BD07}"/>
-                  </a:ext>
-                </a:extLst>
-              </xdr:cNvPr>
-              <xdr:cNvPicPr>
-                <a:picLocks noChangeAspect="1"/>
-              </xdr:cNvPicPr>
-            </xdr:nvPicPr>
-            <xdr:blipFill rotWithShape="1">
-              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-              <a:srcRect t="75912" r="-4286" b="6391"/>
-              <a:stretch>
-                <a:fillRect/>
-              </a:stretch>
-            </xdr:blipFill>
-            <xdr:spPr>
-              <a:xfrm flipH="1">
-                <a:off x="9210676" y="5174341"/>
-                <a:ext cx="225424" cy="224972"/>
-              </a:xfrm>
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
-            </xdr:spPr>
-          </xdr:pic>
-        </xdr:grpSp>
-      </xdr:grpSp>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="36" name="グループ化 35">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8D44BF8-ACBD-430D-8787-2266044639F8}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="9165464" y="3130138"/>
-            <a:ext cx="232156" cy="810811"/>
-            <a:chOff x="9212945" y="4758421"/>
-            <a:chExt cx="219980" cy="824592"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:grpSp>
-          <xdr:nvGrpSpPr>
-            <xdr:cNvPr id="37" name="グループ化 36">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B8FEB8A-CFDF-0DD5-6E59-72E96310EB3C}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGrpSpPr/>
-          </xdr:nvGrpSpPr>
-          <xdr:grpSpPr>
-            <a:xfrm>
-              <a:off x="9210676" y="5174341"/>
-              <a:ext cx="225424" cy="408672"/>
-              <a:chOff x="9210676" y="5174341"/>
-              <a:chExt cx="225424" cy="408672"/>
-            </a:xfrm>
-          </xdr:grpSpPr>
-          <xdr:pic>
-            <xdr:nvPicPr>
-              <xdr:cNvPr id="41" name="図 40">
-                <a:extLst>
-                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42A4C229-A367-7DE7-A6BE-9FCACC178582}"/>
-                  </a:ext>
-                </a:extLst>
-              </xdr:cNvPr>
-              <xdr:cNvPicPr>
-                <a:picLocks noChangeAspect="1"/>
-              </xdr:cNvPicPr>
-            </xdr:nvPicPr>
-            <xdr:blipFill rotWithShape="1">
-              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-              <a:srcRect t="75912" r="-4286" b="6391"/>
-              <a:stretch>
-                <a:fillRect/>
-              </a:stretch>
-            </xdr:blipFill>
-            <xdr:spPr>
-              <a:xfrm flipH="1">
-                <a:off x="9213851" y="5354866"/>
-                <a:ext cx="222249" cy="228147"/>
-              </a:xfrm>
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
-            </xdr:spPr>
-          </xdr:pic>
-          <xdr:pic>
-            <xdr:nvPicPr>
-              <xdr:cNvPr id="42" name="図 41">
-                <a:extLst>
-                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6240F1CA-EF1F-43AF-84A8-AED872292523}"/>
-                  </a:ext>
-                </a:extLst>
-              </xdr:cNvPr>
-              <xdr:cNvPicPr>
-                <a:picLocks noChangeAspect="1"/>
-              </xdr:cNvPicPr>
-            </xdr:nvPicPr>
-            <xdr:blipFill rotWithShape="1">
-              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-              <a:srcRect t="75912" r="-4286" b="6391"/>
-              <a:stretch>
-                <a:fillRect/>
-              </a:stretch>
-            </xdr:blipFill>
-            <xdr:spPr>
-              <a:xfrm flipH="1">
-                <a:off x="9210676" y="5174341"/>
-                <a:ext cx="225424" cy="224972"/>
-              </a:xfrm>
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
-            </xdr:spPr>
-          </xdr:pic>
-        </xdr:grpSp>
-        <xdr:grpSp>
-          <xdr:nvGrpSpPr>
-            <xdr:cNvPr id="38" name="グループ化 37">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96921444-4C15-6954-0EAE-88B69A4A0C2F}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGrpSpPr/>
-          </xdr:nvGrpSpPr>
-          <xdr:grpSpPr>
-            <a:xfrm>
-              <a:off x="9216120" y="4755246"/>
-              <a:ext cx="209549" cy="418197"/>
-              <a:chOff x="9210676" y="5174341"/>
-              <a:chExt cx="225424" cy="408672"/>
-            </a:xfrm>
-          </xdr:grpSpPr>
-          <xdr:pic>
-            <xdr:nvPicPr>
-              <xdr:cNvPr id="39" name="図 38">
-                <a:extLst>
-                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70EE92B0-9679-E525-CF04-C70906B7620C}"/>
-                  </a:ext>
-                </a:extLst>
-              </xdr:cNvPr>
-              <xdr:cNvPicPr>
-                <a:picLocks noChangeAspect="1"/>
-              </xdr:cNvPicPr>
-            </xdr:nvPicPr>
-            <xdr:blipFill rotWithShape="1">
-              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-              <a:srcRect t="75912" r="-4286" b="6391"/>
-              <a:stretch>
-                <a:fillRect/>
-              </a:stretch>
-            </xdr:blipFill>
-            <xdr:spPr>
-              <a:xfrm flipH="1">
-                <a:off x="9213851" y="5354866"/>
-                <a:ext cx="222249" cy="228147"/>
-              </a:xfrm>
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
-            </xdr:spPr>
-          </xdr:pic>
-          <xdr:pic>
-            <xdr:nvPicPr>
-              <xdr:cNvPr id="40" name="図 39">
-                <a:extLst>
-                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CAEDF4E-5B3C-69DF-6858-3F9637402105}"/>
-                  </a:ext>
-                </a:extLst>
-              </xdr:cNvPr>
-              <xdr:cNvPicPr>
-                <a:picLocks noChangeAspect="1"/>
-              </xdr:cNvPicPr>
-            </xdr:nvPicPr>
-            <xdr:blipFill rotWithShape="1">
-              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-              <a:srcRect t="75912" r="-4286" b="6391"/>
-              <a:stretch>
-                <a:fillRect/>
-              </a:stretch>
-            </xdr:blipFill>
-            <xdr:spPr>
-              <a:xfrm flipH="1">
-                <a:off x="9210676" y="5174341"/>
-                <a:ext cx="225424" cy="224972"/>
-              </a:xfrm>
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
-            </xdr:spPr>
-          </xdr:pic>
-        </xdr:grpSp>
-      </xdr:grpSp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>25</xdr:row>
@@ -5291,280 +4674,6 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>51</xdr:col>
-      <xdr:colOff>55356</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>52</xdr:col>
-      <xdr:colOff>1584</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="172" name="グループ化 171">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42493288-82C3-A361-66A9-E9E73B490289}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="9231106" y="2111375"/>
-          <a:ext cx="126145" cy="396875"/>
-          <a:chOff x="9285081" y="2111375"/>
-          <a:chExt cx="127203" cy="431799"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="149" name="図 148">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5774797-6046-EFCF-EF03-7CBAC6D4EA68}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm flipH="1">
-            <a:off x="9288243" y="2111375"/>
-            <a:ext cx="104530" cy="318001"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="150" name="図 149">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F2E7885-1B1F-0DEA-19AF-A682FF08072D}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill rotWithShape="1">
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-          <a:srcRect l="1" t="75912" r="-1"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm flipH="1">
-            <a:off x="9285081" y="2466926"/>
-            <a:ext cx="118814" cy="76248"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="151" name="グループ化 150">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9DB36F4-EE5A-DD7E-6E99-31E8D0A38D52}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="9299139" y="2297765"/>
-            <a:ext cx="113145" cy="196420"/>
-            <a:chOff x="9212945" y="4758421"/>
-            <a:chExt cx="219980" cy="824592"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:grpSp>
-          <xdr:nvGrpSpPr>
-            <xdr:cNvPr id="166" name="グループ化 165">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5DA51CD-F4D6-0D54-029B-C0146497ACBC}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGrpSpPr/>
-          </xdr:nvGrpSpPr>
-          <xdr:grpSpPr>
-            <a:xfrm>
-              <a:off x="9210676" y="5174341"/>
-              <a:ext cx="225424" cy="408672"/>
-              <a:chOff x="9210676" y="5174341"/>
-              <a:chExt cx="225424" cy="408672"/>
-            </a:xfrm>
-          </xdr:grpSpPr>
-          <xdr:pic>
-            <xdr:nvPicPr>
-              <xdr:cNvPr id="170" name="図 169">
-                <a:extLst>
-                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8595DBA-2C87-9541-9B79-EB42D746B519}"/>
-                  </a:ext>
-                </a:extLst>
-              </xdr:cNvPr>
-              <xdr:cNvPicPr>
-                <a:picLocks noChangeAspect="1"/>
-              </xdr:cNvPicPr>
-            </xdr:nvPicPr>
-            <xdr:blipFill rotWithShape="1">
-              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-              <a:srcRect t="75912" r="-4286" b="6391"/>
-              <a:stretch>
-                <a:fillRect/>
-              </a:stretch>
-            </xdr:blipFill>
-            <xdr:spPr>
-              <a:xfrm flipH="1">
-                <a:off x="9213851" y="5354866"/>
-                <a:ext cx="222249" cy="228147"/>
-              </a:xfrm>
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
-            </xdr:spPr>
-          </xdr:pic>
-          <xdr:pic>
-            <xdr:nvPicPr>
-              <xdr:cNvPr id="171" name="図 170">
-                <a:extLst>
-                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6836E95-2A3A-3884-21E3-A99599259417}"/>
-                  </a:ext>
-                </a:extLst>
-              </xdr:cNvPr>
-              <xdr:cNvPicPr>
-                <a:picLocks noChangeAspect="1"/>
-              </xdr:cNvPicPr>
-            </xdr:nvPicPr>
-            <xdr:blipFill rotWithShape="1">
-              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-              <a:srcRect t="75912" r="-4286" b="6391"/>
-              <a:stretch>
-                <a:fillRect/>
-              </a:stretch>
-            </xdr:blipFill>
-            <xdr:spPr>
-              <a:xfrm flipH="1">
-                <a:off x="9210676" y="5174341"/>
-                <a:ext cx="225424" cy="224972"/>
-              </a:xfrm>
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
-            </xdr:spPr>
-          </xdr:pic>
-        </xdr:grpSp>
-        <xdr:grpSp>
-          <xdr:nvGrpSpPr>
-            <xdr:cNvPr id="167" name="グループ化 166">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE32C7E2-7A4D-9348-B206-7B8BF3FDB080}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGrpSpPr/>
-          </xdr:nvGrpSpPr>
-          <xdr:grpSpPr>
-            <a:xfrm>
-              <a:off x="9216120" y="4755246"/>
-              <a:ext cx="209549" cy="418197"/>
-              <a:chOff x="9210676" y="5174341"/>
-              <a:chExt cx="225424" cy="408672"/>
-            </a:xfrm>
-          </xdr:grpSpPr>
-          <xdr:pic>
-            <xdr:nvPicPr>
-              <xdr:cNvPr id="168" name="図 167">
-                <a:extLst>
-                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEFF6C4C-8049-C94F-15FF-40138AED1630}"/>
-                  </a:ext>
-                </a:extLst>
-              </xdr:cNvPr>
-              <xdr:cNvPicPr>
-                <a:picLocks noChangeAspect="1"/>
-              </xdr:cNvPicPr>
-            </xdr:nvPicPr>
-            <xdr:blipFill rotWithShape="1">
-              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-              <a:srcRect t="75912" r="-4286" b="6391"/>
-              <a:stretch>
-                <a:fillRect/>
-              </a:stretch>
-            </xdr:blipFill>
-            <xdr:spPr>
-              <a:xfrm flipH="1">
-                <a:off x="9213851" y="5354866"/>
-                <a:ext cx="222249" cy="228147"/>
-              </a:xfrm>
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
-            </xdr:spPr>
-          </xdr:pic>
-          <xdr:pic>
-            <xdr:nvPicPr>
-              <xdr:cNvPr id="169" name="図 168">
-                <a:extLst>
-                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F0B8B1A-11C2-BA27-5FAF-158B600FDFFC}"/>
-                  </a:ext>
-                </a:extLst>
-              </xdr:cNvPr>
-              <xdr:cNvPicPr>
-                <a:picLocks noChangeAspect="1"/>
-              </xdr:cNvPicPr>
-            </xdr:nvPicPr>
-            <xdr:blipFill rotWithShape="1">
-              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-              <a:srcRect t="75912" r="-4286" b="6391"/>
-              <a:stretch>
-                <a:fillRect/>
-              </a:stretch>
-            </xdr:blipFill>
-            <xdr:spPr>
-              <a:xfrm flipH="1">
-                <a:off x="9210676" y="5174341"/>
-                <a:ext cx="225424" cy="224972"/>
-              </a:xfrm>
-              <a:prstGeom prst="rect">
-                <a:avLst/>
-              </a:prstGeom>
-            </xdr:spPr>
-          </xdr:pic>
-        </xdr:grpSp>
-      </xdr:grpSp>
-    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
@@ -7541,7 +6650,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill rotWithShape="1">
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
           <a:srcRect l="31114" b="2218"/>
           <a:stretch>
             <a:fillRect/>
@@ -8865,7 +7974,7 @@
     <row r="22" spans="2:8" ht="14.25" customHeight="1">
       <c r="B22" s="156" t="str">
         <f ca="1">TEXT(変更来歴!AT2,"yyyy年 mm月 dd日") &amp; " " &amp; 変更来歴!AT3</f>
-        <v>2026年 06月 11日 dr1.2</v>
+        <v>2026年 06月 17日 dr1.3</v>
       </c>
       <c r="C22" s="157"/>
       <c r="D22" s="157"/>
@@ -9939,7 +9048,7 @@
       <c r="AR2" s="160"/>
       <c r="AS2" s="160"/>
       <c r="AT2" s="163">
-        <v>46184</v>
+        <v>46190</v>
       </c>
       <c r="AU2" s="163"/>
       <c r="AV2" s="163"/>
@@ -10009,7 +9118,7 @@
       <c r="AS3" s="160"/>
       <c r="AT3" s="161" t="str">
         <f ca="1">INDIRECT("A" &amp; COUNTA(A7:A39) + 6)</f>
-        <v>dr1.2</v>
+        <v>dr1.3</v>
       </c>
       <c r="AU3" s="161"/>
       <c r="AV3" s="161"/>
@@ -10340,9 +9449,13 @@
       <c r="BA9" s="190"/>
     </row>
     <row r="10" spans="1:53">
-      <c r="A10" s="187"/>
+      <c r="A10" s="187" t="s">
+        <v>149</v>
+      </c>
       <c r="B10" s="187"/>
-      <c r="C10" s="190"/>
+      <c r="C10" s="190" t="s">
+        <v>143</v>
+      </c>
       <c r="D10" s="190"/>
       <c r="E10" s="190"/>
       <c r="F10" s="190"/>
@@ -10356,7 +9469,9 @@
       <c r="N10" s="190"/>
       <c r="O10" s="190"/>
       <c r="P10" s="190"/>
-      <c r="Q10" s="191"/>
+      <c r="Q10" s="191" t="s">
+        <v>150</v>
+      </c>
       <c r="R10" s="190"/>
       <c r="S10" s="190"/>
       <c r="T10" s="190"/>
@@ -10377,11 +9492,15 @@
       <c r="AI10" s="190"/>
       <c r="AJ10" s="190"/>
       <c r="AK10" s="190"/>
-      <c r="AL10" s="197"/>
+      <c r="AL10" s="197">
+        <v>46190</v>
+      </c>
       <c r="AM10" s="187"/>
       <c r="AN10" s="187"/>
       <c r="AO10" s="187"/>
-      <c r="AP10" s="190"/>
+      <c r="AP10" s="190" t="s">
+        <v>29</v>
+      </c>
       <c r="AQ10" s="190"/>
       <c r="AR10" s="190"/>
       <c r="AS10" s="190"/>
@@ -12118,7 +11237,7 @@
       <c r="AU2" s="160"/>
       <c r="AV2" s="163">
         <f ca="1">INDIRECT("変更来歴!AL" &amp; COUNTA(変更来歴!AL7:'変更来歴'!AL39) + 6)</f>
-        <v>46184</v>
+        <v>46190</v>
       </c>
       <c r="AW2" s="161"/>
       <c r="AX2" s="161"/>
@@ -12170,7 +11289,7 @@
       <c r="Z3" s="171"/>
       <c r="AA3" s="183" t="str">
         <f ca="1">MID(CELL("filename"),FIND("]",CELL("filename"))+1,LEN(CELL("filename"))) &amp; "画面"</f>
-        <v>変更来歴画面</v>
+        <v>表紙画面</v>
       </c>
       <c r="AB3" s="183"/>
       <c r="AC3" s="183"/>
@@ -12196,7 +11315,7 @@
       <c r="AU3" s="160"/>
       <c r="AV3" s="161" t="str">
         <f ca="1">INDIRECT("変更来歴!A" &amp; COUNTA(変更来歴!A7:'変更来歴'!A39) + 6)</f>
-        <v>dr1.2</v>
+        <v>dr1.3</v>
       </c>
       <c r="AW3" s="161"/>
       <c r="AX3" s="161"/>
@@ -12210,7 +11329,7 @@
     <row r="5" spans="1:88" ht="13.5" customHeight="1">
       <c r="A5" s="210" t="str">
         <f ca="1">"画面レイアウト"&amp;"("&amp;MID(CELL("filename"),FIND("]",CELL("filename"))+1,LEN(CELL("filename")))&amp;")"</f>
-        <v>画面レイアウト(変更来歴)</v>
+        <v>画面レイアウト(表紙)</v>
       </c>
       <c r="B5" s="211"/>
       <c r="C5" s="211"/>
